--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -1943,7 +1943,7 @@
       </c>
       <c r="K13" s="51" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai</t>
         </is>
       </c>
       <c r="L13" s="51" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -1845,7 +1845,7 @@
       </c>
       <c r="K11" s="45" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai</t>
         </is>
       </c>
       <c r="L11" s="45" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -2254,7 +2254,7 @@
       </c>
       <c r="K20" s="45" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai</t>
         </is>
       </c>
       <c r="L20" s="45" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -2548,7 +2548,7 @@
       </c>
       <c r="K26" s="56" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai</t>
         </is>
       </c>
       <c r="L26" s="56" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K15" s="56" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai</t>
         </is>
       </c>
       <c r="L15" s="56" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -2352,7 +2352,7 @@
       </c>
       <c r="K22" s="56" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai</t>
         </is>
       </c>
       <c r="L22" s="56" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -2090,7 +2090,7 @@
       </c>
       <c r="K16" s="56" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai (draft, perlu review legal)</t>
         </is>
       </c>
       <c r="L16" s="56" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -3104,7 +3104,7 @@
       </c>
       <c r="K38" s="56" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai (manual code review, ZAP dynamic scan belum dijalankan)</t>
         </is>
       </c>
       <c r="L38" s="56" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="K6" s="45" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai (GA4 terpasang, Clarity belum — ID belum diberikan)</t>
         </is>
       </c>
       <c r="L6" s="45" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="K6" s="45" t="inlineStr">
         <is>
-          <t>✅ Selesai (GA4 terpasang, Clarity belum — ID belum diberikan)</t>
+          <t>✅ Selesai</t>
         </is>
       </c>
       <c r="L6" s="45" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -2597,7 +2597,7 @@
       </c>
       <c r="K27" s="51" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai (Sentry sudah live, Uptime Robot perlu setup manual di dashboard)</t>
         </is>
       </c>
       <c r="L27" s="51" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="K10" s="45" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai</t>
         </is>
       </c>
       <c r="L10" s="45" t="inlineStr">

--- a/action_plan.xlsx
+++ b/action_plan.xlsx
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K12" s="51" t="inlineStr">
         <is>
-          <t>⬜ Belum Mulai</t>
+          <t>✅ Selesai</t>
         </is>
       </c>
       <c r="L12" s="51" t="inlineStr">
